--- a/artfynd/A 32849-2023 artfynd.xlsx
+++ b/artfynd/A 32849-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32849-2023 artfynd.xlsx
+++ b/artfynd/A 32849-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2020,6 +2020,725 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>114991529</v>
+      </c>
+      <c r="B14" t="n">
+        <v>94339</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Maden, Vg</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>335151</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6434065</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>114991521</v>
+      </c>
+      <c r="B15" t="n">
+        <v>93979</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Maden, Vg</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>335173</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6434093</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>114991524</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57255</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Maden, Vg</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>335237</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6434154</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Gamla hack</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>114991532</v>
+      </c>
+      <c r="B17" t="n">
+        <v>94339</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Maden, Vg</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>335176</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6434131</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>114991530</v>
+      </c>
+      <c r="B18" t="n">
+        <v>94339</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Maden, Vg</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>335180</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6434207</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>114991531</v>
+      </c>
+      <c r="B19" t="n">
+        <v>94339</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Maden, Vg</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>335151</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6434157</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>114991523</v>
+      </c>
+      <c r="B20" t="n">
+        <v>93979</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Maden, Vg</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>335102</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6434136</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32849-2023 artfynd.xlsx
+++ b/artfynd/A 32849-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2984,6 +2984,117 @@
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129021669</v>
+      </c>
+      <c r="B23" t="n">
+        <v>96239</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Gullringen, Vg</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>335117</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6434075</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>cirka 70 cm i diameter</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32849-2023 artfynd.xlsx
+++ b/artfynd/A 32849-2023 artfynd.xlsx
@@ -2989,7 +2989,7 @@
         <v>129021669</v>
       </c>
       <c r="B23" t="n">
-        <v>96247</v>
+        <v>96252</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 32849-2023 artfynd.xlsx
+++ b/artfynd/A 32849-2023 artfynd.xlsx
@@ -2989,7 +2989,7 @@
         <v>129021669</v>
       </c>
       <c r="B23" t="n">
-        <v>96252</v>
+        <v>96255</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 32849-2023 artfynd.xlsx
+++ b/artfynd/A 32849-2023 artfynd.xlsx
@@ -2989,7 +2989,7 @@
         <v>129021669</v>
       </c>
       <c r="B23" t="n">
-        <v>96255</v>
+        <v>96265</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 32849-2023 artfynd.xlsx
+++ b/artfynd/A 32849-2023 artfynd.xlsx
@@ -2989,7 +2989,7 @@
         <v>129021669</v>
       </c>
       <c r="B23" t="n">
-        <v>96265</v>
+        <v>96272</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 32849-2023 artfynd.xlsx
+++ b/artfynd/A 32849-2023 artfynd.xlsx
@@ -2989,7 +2989,7 @@
         <v>129021669</v>
       </c>
       <c r="B23" t="n">
-        <v>96272</v>
+        <v>96274</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 32849-2023 artfynd.xlsx
+++ b/artfynd/A 32849-2023 artfynd.xlsx
@@ -2989,7 +2989,7 @@
         <v>129021669</v>
       </c>
       <c r="B23" t="n">
-        <v>96274</v>
+        <v>96300</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 32849-2023 artfynd.xlsx
+++ b/artfynd/A 32849-2023 artfynd.xlsx
@@ -2989,7 +2989,7 @@
         <v>129021669</v>
       </c>
       <c r="B23" t="n">
-        <v>96300</v>
+        <v>96301</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 32849-2023 artfynd.xlsx
+++ b/artfynd/A 32849-2023 artfynd.xlsx
@@ -2989,7 +2989,7 @@
         <v>129021669</v>
       </c>
       <c r="B23" t="n">
-        <v>96301</v>
+        <v>96302</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 32849-2023 artfynd.xlsx
+++ b/artfynd/A 32849-2023 artfynd.xlsx
@@ -2989,7 +2989,7 @@
         <v>129021669</v>
       </c>
       <c r="B23" t="n">
-        <v>96302</v>
+        <v>96306</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 32849-2023 artfynd.xlsx
+++ b/artfynd/A 32849-2023 artfynd.xlsx
@@ -2989,7 +2989,7 @@
         <v>129021669</v>
       </c>
       <c r="B23" t="n">
-        <v>96306</v>
+        <v>96308</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 32849-2023 artfynd.xlsx
+++ b/artfynd/A 32849-2023 artfynd.xlsx
@@ -2989,7 +2989,7 @@
         <v>129021669</v>
       </c>
       <c r="B23" t="n">
-        <v>96308</v>
+        <v>96312</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 32849-2023 artfynd.xlsx
+++ b/artfynd/A 32849-2023 artfynd.xlsx
@@ -2989,7 +2989,7 @@
         <v>129021669</v>
       </c>
       <c r="B23" t="n">
-        <v>96312</v>
+        <v>96320</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 32849-2023 artfynd.xlsx
+++ b/artfynd/A 32849-2023 artfynd.xlsx
@@ -2989,7 +2989,7 @@
         <v>129021669</v>
       </c>
       <c r="B23" t="n">
-        <v>96320</v>
+        <v>96323</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 32849-2023 artfynd.xlsx
+++ b/artfynd/A 32849-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3095,6 +3095,213 @@
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129836064</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92913</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>GR, Vg</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>335156</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6434108</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Nära tall på kalkfattig mark.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129836038</v>
+      </c>
+      <c r="B25" t="n">
+        <v>92875</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>GR, Vg</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>335156</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6434108</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32849-2023 artfynd.xlsx
+++ b/artfynd/A 32849-2023 artfynd.xlsx
@@ -3100,7 +3100,7 @@
         <v>129836064</v>
       </c>
       <c r="B24" t="n">
-        <v>92913</v>
+        <v>92917</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>129836038</v>
       </c>
       <c r="B25" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 32849-2023 artfynd.xlsx
+++ b/artfynd/A 32849-2023 artfynd.xlsx
@@ -3100,7 +3100,7 @@
         <v>129836064</v>
       </c>
       <c r="B24" t="n">
-        <v>92917</v>
+        <v>92919</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>129836038</v>
       </c>
       <c r="B25" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 32849-2023 artfynd.xlsx
+++ b/artfynd/A 32849-2023 artfynd.xlsx
@@ -3175,7 +3175,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Nära tall på kalkfattig mark.</t>
+          <t>Nära tall på kalkfattig mark. Artbestämmare Sten Svantesson.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Liv Vikingson, Sten Svantesson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3279,6 +3279,11 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Artbestämmare: Sten Svantesson</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3297,7 +3302,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Liv Vikingson, Sten Svantesson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 32849-2023 artfynd.xlsx
+++ b/artfynd/A 32849-2023 artfynd.xlsx
@@ -3100,7 +3100,7 @@
         <v>129836064</v>
       </c>
       <c r="B24" t="n">
-        <v>92919</v>
+        <v>92922</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>129836038</v>
       </c>
       <c r="B25" t="n">
-        <v>92881</v>
+        <v>92884</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 32849-2023 artfynd.xlsx
+++ b/artfynd/A 32849-2023 artfynd.xlsx
@@ -3100,7 +3100,7 @@
         <v>129836064</v>
       </c>
       <c r="B24" t="n">
-        <v>92922</v>
+        <v>92925</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>129836038</v>
       </c>
       <c r="B25" t="n">
-        <v>92884</v>
+        <v>92887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 32849-2023 artfynd.xlsx
+++ b/artfynd/A 32849-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3100,7 +3100,7 @@
         <v>129836064</v>
       </c>
       <c r="B24" t="n">
-        <v>92925</v>
+        <v>92926</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>129836038</v>
       </c>
       <c r="B25" t="n">
-        <v>92887</v>
+        <v>92888</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3307,6 +3307,226 @@
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130045669</v>
+      </c>
+      <c r="B26" t="n">
+        <v>97669</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lödöse, Maden, Vg</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>335078</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6434124</v>
+      </c>
+      <c r="S26" t="n">
+        <v>100</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Ann-Charlotte Svensson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Ann-Charlotte Svensson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130045579</v>
+      </c>
+      <c r="B27" t="n">
+        <v>97669</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lödöse, Maden, Vg</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>335138</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6434121</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Ann-Charlotte Svensson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Ann-Charlotte Svensson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32849-2023 artfynd.xlsx
+++ b/artfynd/A 32849-2023 artfynd.xlsx
@@ -3100,7 +3100,7 @@
         <v>129836064</v>
       </c>
       <c r="B24" t="n">
-        <v>92926</v>
+        <v>92943</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>129836038</v>
       </c>
       <c r="B25" t="n">
-        <v>92888</v>
+        <v>92905</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>130045669</v>
       </c>
       <c r="B26" t="n">
-        <v>97669</v>
+        <v>97686</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>130045579</v>
       </c>
       <c r="B27" t="n">
-        <v>97669</v>
+        <v>97686</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 32849-2023 artfynd.xlsx
+++ b/artfynd/A 32849-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3100,7 +3100,7 @@
         <v>129836064</v>
       </c>
       <c r="B24" t="n">
-        <v>92959</v>
+        <v>92961</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>129836038</v>
       </c>
       <c r="B25" t="n">
-        <v>92921</v>
+        <v>92923</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>130045669</v>
       </c>
       <c r="B26" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>130045579</v>
       </c>
       <c r="B27" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>130124774</v>
       </c>
       <c r="B29" t="n">
-        <v>96067</v>
+        <v>96069</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3745,6 +3745,205 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>130251438</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57738</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Gullringen, Vg</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>335278</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6434134</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-12-14</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-12-14</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>130251385</v>
+      </c>
+      <c r="B31" t="n">
+        <v>97706</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Gullringen, Vg</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>335248</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6434169</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-12-14</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-12-14</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32849-2023 artfynd.xlsx
+++ b/artfynd/A 32849-2023 artfynd.xlsx
@@ -3100,7 +3100,7 @@
         <v>129836064</v>
       </c>
       <c r="B24" t="n">
-        <v>92961</v>
+        <v>93048</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>129836038</v>
       </c>
       <c r="B25" t="n">
-        <v>92923</v>
+        <v>93010</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>130045669</v>
       </c>
       <c r="B26" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>130045579</v>
       </c>
       <c r="B27" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>130125907</v>
       </c>
       <c r="B28" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>130124774</v>
       </c>
       <c r="B29" t="n">
-        <v>96069</v>
+        <v>96156</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>130251438</v>
       </c>
       <c r="B30" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>130251385</v>
       </c>
       <c r="B31" t="n">
-        <v>97706</v>
+        <v>97793</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 32849-2023 artfynd.xlsx
+++ b/artfynd/A 32849-2023 artfynd.xlsx
@@ -3100,7 +3100,7 @@
         <v>129836064</v>
       </c>
       <c r="B24" t="n">
-        <v>93048</v>
+        <v>92961</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>129836038</v>
       </c>
       <c r="B25" t="n">
-        <v>93010</v>
+        <v>92923</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 32849-2023 artfynd.xlsx
+++ b/artfynd/A 32849-2023 artfynd.xlsx
@@ -3644,7 +3644,7 @@
         <v>130124774</v>
       </c>
       <c r="B29" t="n">
-        <v>96156</v>
+        <v>96159</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>130251385</v>
       </c>
       <c r="B31" t="n">
-        <v>97793</v>
+        <v>97796</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 32849-2023 artfynd.xlsx
+++ b/artfynd/A 32849-2023 artfynd.xlsx
@@ -3532,7 +3532,7 @@
         <v>130125907</v>
       </c>
       <c r="B28" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>130124774</v>
       </c>
       <c r="B29" t="n">
-        <v>96159</v>
+        <v>96185</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>130251438</v>
       </c>
       <c r="B30" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>130251385</v>
       </c>
       <c r="B31" t="n">
-        <v>97796</v>
+        <v>97822</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 32849-2023 artfynd.xlsx
+++ b/artfynd/A 32849-2023 artfynd.xlsx
@@ -3852,7 +3852,7 @@
         <v>130251385</v>
       </c>
       <c r="B31" t="n">
-        <v>97822</v>
+        <v>97823</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 32849-2023 artfynd.xlsx
+++ b/artfynd/A 32849-2023 artfynd.xlsx
@@ -3852,7 +3852,7 @@
         <v>130251385</v>
       </c>
       <c r="B31" t="n">
-        <v>97823</v>
+        <v>97824</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 32849-2023 artfynd.xlsx
+++ b/artfynd/A 32849-2023 artfynd.xlsx
@@ -3751,7 +3751,7 @@
         <v>130251438</v>
       </c>
       <c r="B30" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>130251385</v>
       </c>
       <c r="B31" t="n">
-        <v>97824</v>
+        <v>97826</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 32849-2023 artfynd.xlsx
+++ b/artfynd/A 32849-2023 artfynd.xlsx
@@ -3852,7 +3852,7 @@
         <v>130251385</v>
       </c>
       <c r="B31" t="n">
-        <v>97826</v>
+        <v>97830</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 32849-2023 artfynd.xlsx
+++ b/artfynd/A 32849-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3945,6 +3945,328 @@
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>130875604</v>
+      </c>
+      <c r="B32" t="n">
+        <v>58236</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Gullringen, Vg</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>335117</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6434075</v>
+      </c>
+      <c r="S32" t="n">
+        <v>75</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Hörs regelbundet i hela skogen.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>130875484</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58236</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Maden, Vg</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>335315</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6434114</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Ann-Charlotte Svensson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Ann-Charlotte Svensson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>130875510</v>
+      </c>
+      <c r="B34" t="n">
+        <v>58726</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Gullringen, Vg</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>335156</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6434108</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32849-2023 artfynd.xlsx
+++ b/artfynd/A 32849-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4267,6 +4267,213 @@
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>130876157</v>
+      </c>
+      <c r="B35" t="n">
+        <v>97845</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lid, Vg</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>335074</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6434013</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Ann-Charlotte Svensson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Ann-Charlotte Svensson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>130882077</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57861</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Gullringen, Vg</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>335197</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6434119</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32849-2023 artfynd.xlsx
+++ b/artfynd/A 32849-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111719367</v>
+        <v>111719368</v>
       </c>
       <c r="B2" t="n">
-        <v>94173</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2590</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Låga, Vg</t>
+          <t>Skogsgolv, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>335111</v>
+        <v>335093</v>
       </c>
       <c r="R2" t="n">
-        <v>6434078</v>
+        <v>6434100</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På ca 2dm bred låga</t>
+          <t>Stor kudde som längre in i landet hade indikerat höga naturvärden men här på västkusten är arten för vanlig. Spridd i hela skogen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111719379</v>
+        <v>111902423</v>
       </c>
       <c r="B3" t="n">
-        <v>93067</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,37 +788,49 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Granrot, Vg</t>
+          <t>Lid, norr om, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>335114</v>
+        <v>335257</v>
       </c>
       <c r="R3" t="n">
-        <v>6434212</v>
+        <v>6434119</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,17 +854,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Här och var i hela skogen</t>
+          <t>En ca 12-15 cm hög tuva. 35 cm lång och 25 cm bred.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,79 +873,79 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111719371</v>
+        <v>111902431</v>
       </c>
       <c r="B4" t="n">
-        <v>56414</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tallhögstubbe, Vg</t>
+          <t>Lid, norr om, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>335100</v>
+        <v>335308</v>
       </c>
       <c r="R4" t="n">
-        <v>6434123</v>
+        <v>6434084</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,17 +969,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Endast 5 cm hög och 20 cm lång.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,33 +988,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111719369</v>
+        <v>114991529</v>
       </c>
       <c r="B5" t="n">
-        <v>94173</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1020,34 +1018,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2590</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Låga, Vg</t>
+          <t>Maden, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>335096</v>
+        <v>335151</v>
       </c>
       <c r="R5" t="n">
-        <v>6434106</v>
+        <v>6434065</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,17 +1072,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På låga, kollekt bekräftad i stereolupp.</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,27 +1092,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111719368</v>
+        <v>114991530</v>
       </c>
       <c r="B6" t="n">
-        <v>93388</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1147,14 +1135,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skogsgolv, Vg</t>
+          <t>Maden, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>335092</v>
+        <v>335180</v>
       </c>
       <c r="R6" t="n">
-        <v>6434100</v>
+        <v>6434208</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,17 +1169,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Stor kudde som längre in i landet hade indikerat höga naturvärden men här på västkusten är arten för vanlig. Spridd i hela skogen.</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1206,27 +1189,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111719378</v>
+        <v>114991531</v>
       </c>
       <c r="B7" t="n">
-        <v>57580</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1234,34 +1212,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208249</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skog, Vg</t>
+          <t>Maden, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>335118</v>
+        <v>335151</v>
       </c>
       <c r="R7" t="n">
-        <v>6434196</v>
+        <v>6434157</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1288,17 +1266,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Vanlig i hela området</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1313,27 +1286,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111719362</v>
+        <v>114991532</v>
       </c>
       <c r="B8" t="n">
-        <v>93171</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1341,34 +1309,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2818</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stubbe, Vg</t>
+          <t>Maden, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>335121</v>
+        <v>335176</v>
       </c>
       <c r="R8" t="n">
-        <v>6434212</v>
+        <v>6434131</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1395,17 +1363,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På stubbe i norra delen av skog nära öppen gräsmark. Endast litet bestånd, p.g.a kraftigt regn svår att identifiera i fält men kollekt bekräftat i stereolupp.</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1420,73 +1383,68 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111719366</v>
+        <v>129021669</v>
       </c>
       <c r="B9" t="n">
-        <v>56414</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Grov tallraka, Vg</t>
+          <t>Gullringen, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>335187</v>
+        <v>335117</v>
       </c>
       <c r="R9" t="n">
-        <v>6434099</v>
+        <v>6434075</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1510,17 +1468,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>cirka 70 cm i diameter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,33 +1487,29 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111902452</v>
+        <v>115245481</v>
       </c>
       <c r="B10" t="n">
-        <v>90443</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1563,48 +1517,49 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4740</v>
+        <v>2569</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sotriska</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius lignyotus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lid, norr om, Vg</t>
+          <t>Lödöse, Maden, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>335290</v>
+        <v>335138</v>
       </c>
       <c r="R10" t="n">
-        <v>6434131</v>
+        <v>6434121</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1628,17 +1583,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2024-03-17</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Växte i en blandskog med tall, gran, ek och vårtbjörk. Naturskogsartat.</t>
+          <t>2024-03-17</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1654,27 +1614,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111902423</v>
+        <v>111719367</v>
       </c>
       <c r="B11" t="n">
-        <v>93553</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1682,49 +1637,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>2590</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lid, norr om, Vg</t>
+          <t>Låga, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>335257</v>
+        <v>335111</v>
       </c>
       <c r="R11" t="n">
-        <v>6434119</v>
+        <v>6434079</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1748,17 +1691,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>En ca 12-15 cm hög tuva. 35 cm lång och 25 cm bred.</t>
+          <t>På ca 2dm bred låga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1767,73 +1710,63 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112009075</v>
+        <v>111719369</v>
       </c>
       <c r="B12" t="n">
-        <v>56446</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>2590</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gullringen, Vg</t>
+          <t>Låga, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>335112</v>
+        <v>335097</v>
       </c>
       <c r="R12" t="n">
-        <v>6434077</v>
+        <v>6434106</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1860,27 +1793,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>19:33</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>19:33</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Spår efter hack av spillkråka.</t>
+          <t>På låga, kollekt bekräftad i stereolupp.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1895,73 +1818,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ingela Eriksson</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ingela Eriksson</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112009028</v>
+        <v>111719379</v>
       </c>
       <c r="B13" t="n">
-        <v>56446</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gullringen 116, Vg</t>
+          <t>Granrot, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>335206</v>
+        <v>335114</v>
       </c>
       <c r="R13" t="n">
-        <v>6434099</v>
+        <v>6434212</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1985,17 +1895,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Spår efter hack från spillkråka.</t>
+          <t>Här och var i hela skogen</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2010,27 +1920,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ingela Eriksson</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ingela Eriksson</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>114991529</v>
+        <v>114991521</v>
       </c>
       <c r="B14" t="n">
-        <v>94429</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2038,21 +1943,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2180</v>
+        <v>2810</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2062,10 +1967,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>335151</v>
+        <v>335173</v>
       </c>
       <c r="R14" t="n">
-        <v>6434065</v>
+        <v>6434093</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,15 +2029,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>114991530</v>
+        <v>114991522</v>
       </c>
       <c r="B15" t="n">
-        <v>94429</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2140,21 +2040,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2180</v>
+        <v>2810</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2164,10 +2064,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>335180</v>
+        <v>335112</v>
       </c>
       <c r="R15" t="n">
-        <v>6434208</v>
+        <v>6434242</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2226,15 +2126,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>114991521</v>
+        <v>114991523</v>
       </c>
       <c r="B16" t="n">
-        <v>94069</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2266,10 +2161,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>335173</v>
+        <v>335102</v>
       </c>
       <c r="R16" t="n">
-        <v>6434093</v>
+        <v>6434136</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2328,15 +2223,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>114991523</v>
+        <v>126112333</v>
       </c>
       <c r="B17" t="n">
-        <v>94069</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2368,13 +2258,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>335102</v>
+        <v>335085</v>
       </c>
       <c r="R17" t="n">
-        <v>6434136</v>
+        <v>6434217</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2398,12 +2288,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2418,65 +2318,60 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>114991524</v>
+        <v>130124774</v>
       </c>
       <c r="B18" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Maden, Vg</t>
+          <t>Maden, Maden, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>335237</v>
+        <v>335109</v>
       </c>
       <c r="R18" t="n">
-        <v>6434154</v>
+        <v>6434137</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2500,17 +2395,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2025-12-14</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Gamla hack</t>
+          <t>2025-12-14</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2525,27 +2425,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Mats Eriksson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Mats Eriksson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>114991532</v>
+        <v>111719362</v>
       </c>
       <c r="B19" t="n">
-        <v>94429</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2553,34 +2448,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>2818</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Maden, Vg</t>
+          <t>Stubbe, Vg</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>335176</v>
+        <v>335121</v>
       </c>
       <c r="R19" t="n">
-        <v>6434131</v>
+        <v>6434211</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2607,12 +2502,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2023-08-26</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På stubbe i norra delen av skog nära öppen gräsmark. Endast litet bestånd, p.g.a kraftigt regn svår att identifiera i fält men kollekt bekräftat i stereolupp.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2627,65 +2527,63 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>114991531</v>
+        <v>129836038</v>
       </c>
       <c r="B20" t="n">
-        <v>94429</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Maden, Vg</t>
+          <t>GR, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>335151</v>
+        <v>335156</v>
       </c>
       <c r="R20" t="n">
-        <v>6434157</v>
+        <v>6434108</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2709,12 +2607,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Artbestämmare: Sten Svantesson</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2723,33 +2626,29 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Liv Vikingson, Sten Svantesson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>115245481</v>
+        <v>111902452</v>
       </c>
       <c r="B21" t="n">
-        <v>95923</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92836</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2757,49 +2656,48 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2569</v>
+        <v>4740</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Sotriska</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Lactarius lignyotus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lödöse, Maden, Vg</t>
+          <t>Lid, norr om, Vg</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>335138</v>
+        <v>335290</v>
       </c>
       <c r="R21" t="n">
-        <v>6434121</v>
+        <v>6434131</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2823,22 +2721,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Växte i en blandskog med tall, gran, ek och vårtbjörk. Naturskogsartat.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2854,27 +2747,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>115245822</v>
+        <v>129836064</v>
       </c>
       <c r="B22" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2882,45 +2770,40 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lödöse, Maden, Vg</t>
+          <t>GR, Vg</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>335201</v>
+        <v>335156</v>
       </c>
       <c r="R22" t="n">
-        <v>6434230</v>
+        <v>6434108</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2944,22 +2827,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Nära tall på kalkfattig mark. Artbestämmare Sten Svantesson.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2968,28 +2846,29 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Liv Vikingson, Sten Svantesson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129021669</v>
+        <v>111719366</v>
       </c>
       <c r="B23" t="n">
-        <v>96323</v>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2997,45 +2876,45 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gullringen, Vg</t>
+          <t>Grov tallraka, Vg</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>335117</v>
+        <v>335188</v>
       </c>
       <c r="R23" t="n">
-        <v>6434075</v>
+        <v>6434099</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3059,17 +2938,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>cirka 70 cm i diameter</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3078,70 +2957,74 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129836064</v>
+        <v>111719371</v>
       </c>
       <c r="B24" t="n">
-        <v>93048</v>
+        <v>57950</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>GR, Vg</t>
+          <t>Tallhögstubbe, Vg</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>335156</v>
+        <v>335100</v>
       </c>
       <c r="R24" t="n">
-        <v>6434108</v>
+        <v>6434123</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3165,17 +3048,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Nära tall på kalkfattig mark. Artbestämmare Sten Svantesson.</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3184,29 +3067,28 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Liv Vikingson, Sten Svantesson</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129836038</v>
+        <v>112008325</v>
       </c>
       <c r="B25" t="n">
-        <v>93010</v>
+        <v>57950</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3214,37 +3096,38 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>GR, Vg</t>
+          <t>Gullringen 116, Vg</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>335156</v>
+        <v>335206</v>
       </c>
       <c r="R25" t="n">
-        <v>6434108</v>
+        <v>6434100</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3271,17 +3154,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Artbestämmare: Sten Svantesson</t>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3290,29 +3178,28 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liv Vikingson, Sten Svantesson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130045669</v>
+        <v>112009075</v>
       </c>
       <c r="B26" t="n">
-        <v>97791</v>
+        <v>57950</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3320,49 +3207,41 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lödöse, Maden, Vg</t>
+          <t>Gullringen, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>335078</v>
+        <v>335112</v>
       </c>
       <c r="R26" t="n">
-        <v>6434124</v>
+        <v>6434077</v>
       </c>
       <c r="S26" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3386,12 +3265,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>19:33</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Spår efter hack av spillkråka.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3400,29 +3294,28 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130045579</v>
+        <v>114991524</v>
       </c>
       <c r="B27" t="n">
-        <v>97791</v>
+        <v>57950</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3430,46 +3323,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lödöse, Maden, Vg</t>
+          <t>Maden, Vg</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>335138</v>
+        <v>335237</v>
       </c>
       <c r="R27" t="n">
-        <v>6434121</v>
+        <v>6434154</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3496,12 +3377,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Gamla hack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3510,33 +3396,32 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130125907</v>
+        <v>115245822</v>
       </c>
       <c r="B28" t="n">
-        <v>57849</v>
+        <v>57950</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3558,19 +3443,27 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Maden, Maden, Vg</t>
+          <t>Lödöse, Maden, Vg</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>335161</v>
+        <v>335201</v>
       </c>
       <c r="R28" t="n">
-        <v>6434233</v>
+        <v>6434230</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3594,27 +3487,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:36</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3629,22 +3517,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130124774</v>
+        <v>130125907</v>
       </c>
       <c r="B29" t="n">
-        <v>96185</v>
+        <v>57950</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3652,21 +3540,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3676,13 +3564,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>335109</v>
+        <v>335161</v>
       </c>
       <c r="R29" t="n">
-        <v>6434137</v>
+        <v>6434233</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3711,7 +3599,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3721,7 +3609,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3751,11 +3644,11 @@
         <v>130251438</v>
       </c>
       <c r="B30" t="n">
-        <v>57851</v>
+        <v>57950</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3849,10 +3742,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130251385</v>
+        <v>130882077</v>
       </c>
       <c r="B31" t="n">
-        <v>97830</v>
+        <v>57950</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3860,23 +3753,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>224363</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3884,13 +3785,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>335248</v>
+        <v>335197</v>
       </c>
       <c r="R31" t="n">
-        <v>6434169</v>
+        <v>6434119</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3914,12 +3815,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3928,7 +3829,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3947,10 +3847,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130875604</v>
+        <v>111719376</v>
       </c>
       <c r="B32" t="n">
-        <v>58256</v>
+        <v>58327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3976,27 +3876,19 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gullringen, Vg</t>
+          <t>Skog, Vg</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>335117</v>
+        <v>335103</v>
       </c>
       <c r="R32" t="n">
-        <v>6434075</v>
+        <v>6434182</v>
       </c>
       <c r="S32" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4020,17 +3912,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Hörs regelbundet i hela skogen.</t>
+          <t>Sjungande kungsfåglar här och var i hela skogen</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4045,12 +3937,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4060,7 +3952,7 @@
         <v>130875484</v>
       </c>
       <c r="B33" t="n">
-        <v>58256</v>
+        <v>58327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4150,22 +4042,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130875510</v>
+        <v>130875604</v>
       </c>
       <c r="B34" t="n">
-        <v>58746</v>
+        <v>58327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4173,32 +4065,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>208249</v>
+        <v>103015</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4206,13 +4097,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>335156</v>
+        <v>335117</v>
       </c>
       <c r="R34" t="n">
-        <v>6434108</v>
+        <v>6434075</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4244,13 +4135,17 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Hörs regelbundet i hela skogen.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4269,10 +4164,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130876157</v>
+        <v>111719365</v>
       </c>
       <c r="B35" t="n">
-        <v>97880</v>
+        <v>58817</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4280,41 +4175,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>208249</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lid, Vg</t>
+          <t>Mossekant, Vg</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>335074</v>
+        <v>335258</v>
       </c>
       <c r="R35" t="n">
-        <v>6434013</v>
+        <v>6434049</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4338,12 +4229,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2023-08-26</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Vanlig i hela området</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4352,72 +4248,63 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130882077</v>
+        <v>111719378</v>
       </c>
       <c r="B36" t="n">
-        <v>57881</v>
+        <v>58817</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>208249</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gullringen, Vg</t>
+          <t>Skog, Vg</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>335197</v>
+        <v>335118</v>
       </c>
       <c r="R36" t="n">
-        <v>6434119</v>
+        <v>6434197</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4444,12 +4331,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2023-08-26</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Vanlig i hela området</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4464,15 +4356,639 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>130875510</v>
+      </c>
+      <c r="B37" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Gullringen, Vg</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>335156</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6434108</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
           <t>Liv Vikingson</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
+      <c r="AX37" t="inlineStr">
         <is>
           <t>Liv Vikingson</t>
         </is>
       </c>
-      <c r="AY36" t="inlineStr"/>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>114991525</v>
+      </c>
+      <c r="B38" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Maden, Vg</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>335131</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6434003</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>130045579</v>
+      </c>
+      <c r="B39" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lödöse, Maden, Vg</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>335138</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6434121</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Anna Svensson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Anna Svensson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>130045669</v>
+      </c>
+      <c r="B40" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lödöse, Maden, Vg</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>335078</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6434124</v>
+      </c>
+      <c r="S40" t="n">
+        <v>100</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Anna Svensson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Anna Svensson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>130876157</v>
+      </c>
+      <c r="B41" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Lid, Vg</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>335074</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6434013</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Anna Svensson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Anna Svensson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>130251385</v>
+      </c>
+      <c r="B42" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Gullringen, Vg</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>335248</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6434169</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-12-14</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-12-14</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32849-2023 artfynd.xlsx
+++ b/artfynd/A 32849-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AZ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111719368</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111902423</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1004,6 +1019,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111902431</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1101,6 +1121,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114991529</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1198,6 +1223,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114991530</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1295,6 +1325,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114991531</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1392,6 +1427,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114991532</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1503,6 +1543,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129021669</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1623,6 +1668,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115245481</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1725,6 +1775,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111719367</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1827,6 +1882,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111719369</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1929,6 +1989,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111719379</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2026,6 +2091,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114991521</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2123,6 +2193,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114991522</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2220,6 +2295,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114991523</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2327,6 +2407,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126112333</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2434,6 +2519,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130124774</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2536,6 +2626,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111719362</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2642,6 +2737,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129836038</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2756,6 +2856,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111902452</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2862,6 +2967,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129836064</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2972,6 +3082,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111719366</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3082,6 +3197,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111719371</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3193,6 +3313,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112008325</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3309,6 +3434,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112009075</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3411,6 +3541,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114991524</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3526,6 +3661,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115245822</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3638,6 +3778,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130125907</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3739,6 +3884,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130251438</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3844,6 +3994,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130882077</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3946,6 +4101,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111719376</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4051,6 +4211,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130875484</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4161,6 +4326,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130875604</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4263,6 +4433,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111719365</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4365,6 +4540,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111719378</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4472,6 +4652,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130875510</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4569,6 +4754,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114991525</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4679,6 +4869,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130045579</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4789,6 +4984,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130045669</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4891,6 +5091,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130876157</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4989,8 +5194,56 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130251385</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>